--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487742_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487742_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2584</v>
+        <v>5.874</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8856</v>
+        <v>6.4466</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.6271</v>
+        <v>-0.5726</v>
       </c>
       <c r="G2" t="n">
         <v>4.9102</v>
@@ -610,13 +610,13 @@
         <v>1.3582</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9338</v>
+        <v>-0.3182</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.775</v>
+        <v>-0.214</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1588</v>
+        <v>-0.1043</v>
       </c>
       <c r="V2" t="n">
         <v>0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8178</v>
+        <v>1.133</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2692</v>
+        <v>0.1296</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5486</v>
+        <v>1.0035</v>
       </c>
       <c r="G3" t="n">
         <v>-2.5685</v>
@@ -688,13 +688,13 @@
         <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4547</v>
+        <v>0.77</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1664</v>
+        <v>1.0268</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2883</v>
+        <v>-0.2568</v>
       </c>
       <c r="V3" t="n">
         <v>3.1257</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. GARCIA GALLARDO</t>
+          <t>P. BARCALA BELTRAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4079</v>
+        <v>0.268</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7562</v>
+        <v>-0.0672</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3483</v>
+        <v>0.3352</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.5358</v>
+        <v>1.1131</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2623</v>
+        <v>2.0473</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2734</v>
+        <v>-0.9343</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.093</v>
+        <v>-0.0041</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0793</v>
+        <v>1.3306</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.1723</v>
+        <v>-1.3347</v>
       </c>
       <c r="M4" t="n">
-        <v>-4.4428</v>
+        <v>1.1172</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.3416</v>
+        <v>0.7168</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1011</v>
+        <v>0.4004</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3284</v>
+        <v>0.3881</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8597</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>4.8193</v>
+        <v>-0.0631</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9596</v>
+        <v>0.0538</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7257</v>
+        <v>-1.2239</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.7257</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="5">
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BARCALA BELTRAN</t>
+          <t>D. PETIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3654</v>
+        <v>-0.3932</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4281</v>
+        <v>-0.7963</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0626</v>
+        <v>0.4031</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1131</v>
+        <v>-1.272</v>
       </c>
       <c r="H6" t="n">
-        <v>2.0473</v>
+        <v>-1.0051</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9343</v>
+        <v>-0.2669</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0041</v>
+        <v>-1.0545</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3306</v>
+        <v>-0.3872</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3347</v>
+        <v>-0.6673</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1172</v>
+        <v>-0.2175</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7168</v>
+        <v>-0.6179</v>
       </c>
       <c r="O6" t="n">
         <v>0.4004</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6427</v>
+        <v>0.0367</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.424</v>
+        <v>0.2582</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2187</v>
+        <v>-0.2215</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2239</v>
+        <v>0.066</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2239</v>
+        <v>0.066</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. PETIT</t>
+          <t>A. FERNANDEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.921</v>
+        <v>-0.6663</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2968</v>
+        <v>1.077</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3758</v>
+        <v>-1.7432</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.272</v>
+        <v>0.1152</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0051</v>
+        <v>0.4399</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2669</v>
+        <v>-0.3248</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0545</v>
+        <v>1.1673</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3872</v>
+        <v>0.5355</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6673</v>
+        <v>0.6318</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2175</v>
+        <v>-1.0521</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6179</v>
+        <v>-0.0956</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4004</v>
+        <v>-0.9565</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.491</v>
+        <v>-0.4397</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2423</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2488</v>
+        <v>-0.3494</v>
       </c>
       <c r="V7" t="n">
-        <v>0.066</v>
+        <v>-1.506</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.066</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ SANCHEZ</t>
+          <t>I. GARCIA GALLARDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1178</v>
+        <v>-1.459</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8162</v>
+        <v>0.8348</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.934</v>
+        <v>-2.2938</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1152</v>
+        <v>-4.5358</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4399</v>
+        <v>-2.2623</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3248</v>
+        <v>-2.2734</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1673</v>
+        <v>-0.093</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5355</v>
+        <v>1.0793</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6318</v>
+        <v>-1.1723</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0521</v>
+        <v>-4.4428</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0956</v>
+        <v>-3.3416</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9565</v>
+        <v>-1.1011</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>2.3284</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8912</v>
+        <v>0.9928</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3511</v>
+        <v>1.8979</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5401</v>
+        <v>-0.9051</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.506</v>
+        <v>0.7257</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.506</v>
+        <v>0.7257</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5791</v>
+        <v>-2.4158</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2242</v>
+        <v>-1.1426</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3549</v>
+        <v>-1.2731</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2691</v>
@@ -1156,13 +1156,13 @@
         <v>1.9403</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0655</v>
+        <v>0.0978</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8759</v>
+        <v>0.9575</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.9414</v>
+        <v>-0.8597</v>
       </c>
       <c r="V9" t="n">
         <v>0.7257</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1404</v>
+        <v>-3.8251</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.778</v>
+        <v>-1.5172</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3624</v>
+        <v>-2.3079</v>
       </c>
       <c r="G10" t="n">
         <v>-1.995</v>
@@ -1234,13 +1234,13 @@
         <v>0.194</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1155</v>
+        <v>-0.8002</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4845</v>
+        <v>-0.2238</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.631</v>
+        <v>-0.5765</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.8159</v>
+        <v>-5.276</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3553</v>
+        <v>-1.7337</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4605</v>
+        <v>-3.5423</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6999</v>
@@ -1312,13 +1312,13 @@
         <v>1.7463</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.9219</v>
+        <v>-1.3821</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.005</v>
+        <v>-0.3833</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.917</v>
+        <v>-0.9987</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.4574</v>
+        <v>-8.2441</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.222200000000001</v>
+        <v>-6.8999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2351</v>
+        <v>-1.3442</v>
       </c>
       <c r="G12" t="n">
         <v>-5.3968</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5161</v>
+        <v>-0.3028</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7145</v>
+        <v>0.6079</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8017</v>
+        <v>-0.9107</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2161</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-16.151</v>
+        <v>-15.2426</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1737</v>
+        <v>-5.265199999999999</v>
       </c>
       <c r="F13" t="n">
         <v>-9.9771</v>
@@ -1441,7 +1441,7 @@
         <v>-12.0677</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2838999999999987</v>
+        <v>-0.2838999999999996</v>
       </c>
       <c r="K13" t="n">
         <v>8.280099999999999</v>
@@ -1459,7 +1459,7 @@
         <v>-3.5035</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9702000000000006</v>
+        <v>0.9702000000000002</v>
       </c>
       <c r="Q13" t="n">
         <v>-13.5823</v>
@@ -1468,13 +1468,13 @@
         <v>14.5524</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6637</v>
+        <v>-1.7554</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5624</v>
+        <v>3.470999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.2264</v>
+        <v>-5.226500000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.3672</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.121</v>
+        <v>7.3546</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5679</v>
+        <v>4.2676</v>
       </c>
       <c r="F14" t="n">
-        <v>3.5531</v>
+        <v>3.087</v>
       </c>
       <c r="G14" t="n">
         <v>5.7336</v>
@@ -1546,13 +1546,13 @@
         <v>2.7164</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6113</v>
+        <v>0.8448</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2393</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.372</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6631</v>
+        <v>3.7625</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8665</v>
+        <v>2.4151</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7966</v>
+        <v>1.3474</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6973</v>
+        <v>5.6473</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6585</v>
+        <v>2.091</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0388</v>
+        <v>3.5563</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4955</v>
+        <v>5.2834</v>
       </c>
       <c r="K15" t="n">
-        <v>3.036</v>
+        <v>3.312</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5405</v>
+        <v>1.9715</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2018</v>
+        <v>0.3639</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3775</v>
+        <v>-1.221</v>
       </c>
       <c r="O15" t="n">
-        <v>1.5793</v>
+        <v>1.5849</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.8806</v>
+        <v>-2.9105</v>
       </c>
       <c r="R15" t="n">
-        <v>2.7164</v>
+        <v>1.9403</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8001</v>
+        <v>0.357</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0278</v>
+        <v>0.7018</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2276</v>
+        <v>-0.3448</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3299</v>
+        <v>-1.2716</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2239</v>
+        <v>-0.6597</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.894</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.571</v>
+        <v>3.7506</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0152</v>
+        <v>3.816</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4442</v>
+        <v>-0.0654</v>
       </c>
       <c r="G16" t="n">
         <v>2.035</v>
@@ -1702,13 +1702,13 @@
         <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3282</v>
+        <v>-0.1486</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7874</v>
+        <v>0.0134</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.162</v>
       </c>
       <c r="V16" t="n">
         <v>0.894</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2582</v>
+        <v>3.093</v>
       </c>
       <c r="E17" t="n">
-        <v>1.314</v>
+        <v>1.1658</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9442</v>
+        <v>1.9272</v>
       </c>
       <c r="G17" t="n">
-        <v>5.6473</v>
+        <v>2.6973</v>
       </c>
       <c r="H17" t="n">
-        <v>2.091</v>
+        <v>1.6585</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5563</v>
+        <v>1.0388</v>
       </c>
       <c r="J17" t="n">
-        <v>5.2834</v>
+        <v>2.4955</v>
       </c>
       <c r="K17" t="n">
-        <v>3.312</v>
+        <v>3.036</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9715</v>
+        <v>-0.5405</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3639</v>
+        <v>0.2018</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.221</v>
+        <v>-1.3775</v>
       </c>
       <c r="O17" t="n">
-        <v>1.5849</v>
+        <v>1.5793</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9105</v>
+        <v>-3.8806</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9403</v>
+        <v>2.7164</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1473</v>
+        <v>1.2301</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3993</v>
+        <v>1.3271</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.748</v>
+        <v>-0.097</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2716</v>
+        <v>0.3299</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6597</v>
+        <v>1.2239</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6119</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. LAGNIEZ</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5615</v>
+        <v>1.4183</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3178</v>
+        <v>0.1347</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2437</v>
+        <v>1.2837</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8334</v>
+        <v>-1.9004</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4251</v>
+        <v>-1.8142</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2585</v>
+        <v>-0.0862</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6736</v>
+        <v>-1.7248</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0824</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5911999999999999</v>
+        <v>-1.1317</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1598</v>
+        <v>-0.1756</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5075</v>
+        <v>-1.221</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6673</v>
+        <v>1.0454</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5821</v>
+        <v>2.1344</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8058</v>
+        <v>0.3665</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3039</v>
+        <v>1.0416</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5018</v>
+        <v>-0.6751</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6597</v>
+        <v>1.788</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6597</v>
+        <v>1.788</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>N. LAGNIEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.4038</v>
+        <v>1.2406</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6352</v>
+        <v>0.2177</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7685999999999999</v>
+        <v>1.0229</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9004</v>
+        <v>0.8334</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8142</v>
+        <v>-0.4251</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0862</v>
+        <v>1.2585</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.7248</v>
+        <v>0.6736</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0824</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.1317</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1756</v>
+        <v>0.1598</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.221</v>
+        <v>-0.5075</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0454</v>
+        <v>0.6673</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1642</v>
+        <v>0.5821</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3519</v>
+        <v>0.4848</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5421</v>
+        <v>0.2038</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1902</v>
+        <v>0.281</v>
       </c>
       <c r="V19" t="n">
-        <v>1.788</v>
+        <v>-0.6597</v>
       </c>
       <c r="W19" t="n">
-        <v>1.788</v>
+        <v>-0.6597</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>M. MANGUE NVOMO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.102</v>
+        <v>0.0325</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2055</v>
+        <v>0.1826</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3075</v>
+        <v>-0.1501</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2136</v>
+        <v>-0.865</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4105</v>
+        <v>-0.9573</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1969</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7207</v>
+        <v>-0.291</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6395</v>
+        <v>-0.2554</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.0356</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5071</v>
+        <v>-0.574</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.229</v>
+        <v>-0.7019</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2781</v>
+        <v>0.1279</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3582</v>
+        <v>0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0426</v>
+        <v>0.4214</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4251</v>
+        <v>0.1915</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3824</v>
+        <v>0.2299</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. MANGUE NVOMO</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4012</v>
+        <v>-0.1326</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1177</v>
+        <v>-0.0948</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2836</v>
+        <v>-0.0377</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.865</v>
+        <v>1.2136</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9573</v>
+        <v>1.4105</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09229999999999999</v>
+        <v>-0.1969</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.291</v>
+        <v>1.7207</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2554</v>
+        <v>1.6395</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0356</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.574</v>
+        <v>-0.5071</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7019</v>
+        <v>-0.229</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1279</v>
+        <v>-0.2781</v>
       </c>
       <c r="P21" t="n">
-        <v>0.194</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0123</v>
+        <v>0.0121</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1088</v>
+        <v>0.1248</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0965</v>
+        <v>-0.1127</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9244</v>
+        <v>-3.0339</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8271</v>
+        <v>-2.1274</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0973</v>
+        <v>-0.9065</v>
       </c>
       <c r="G22" t="n">
         <v>0.4297</v>
@@ -2170,13 +2170,13 @@
         <v>0.7761</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5399</v>
+        <v>0.4304</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9836</v>
+        <v>0.6833</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4437</v>
+        <v>-0.2529</v>
       </c>
       <c r="V22" t="n">
         <v>-2.7298</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>16.151</v>
+        <v>17.48560000000001</v>
       </c>
       <c r="E23" t="n">
         <v>9.977300000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>6.1736</v>
+        <v>7.508500000000001</v>
       </c>
       <c r="G23" t="n">
         <v>15.8245</v>
@@ -2233,10 +2233,10 @@
         <v>0.2839</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.280000000000001</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>8.563700000000001</v>
+        <v>8.563699999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-0.9702000000000002</v>
@@ -2248,13 +2248,13 @@
         <v>13.5821</v>
       </c>
       <c r="S23" t="n">
-        <v>2.6638</v>
+        <v>3.998499999999999</v>
       </c>
       <c r="T23" t="n">
         <v>5.2263</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.562399999999999</v>
+        <v>-1.2278</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3671</v>
